--- a/MiniTemplate/Datas/convertGroup.xlsx
+++ b/MiniTemplate/Datas/convertGroup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28785" windowHeight="12975"/>
+    <workbookView windowWidth="21000" windowHeight="7485"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -62,7 +62,7 @@
     <t>兑换商人名称</t>
   </si>
   <si>
-    <t>武器兑换商</t>
+    <t>装备兑换商</t>
   </si>
   <si>
     <t>药水兑换商</t>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>[翡翠林海]宝藏兑换商</t>
+  </si>
+  <si>
+    <t>[翡翠林海]装备兑换商</t>
   </si>
 </sst>
 </file>
@@ -1126,6 +1129,12 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="G10" s="2"/>
     </row>
